--- a/content_forms/009_media_upload_for_synchronization--content_forms.xlsx
+++ b/content_forms/009_media_upload_for_synchronization--content_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1129,8 +1129,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Audio'}</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'image'}</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Image'}</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -1209,12 +1209,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1243,12 +1243,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1328,12 +1328,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1345,12 +1345,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1379,12 +1379,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1396,12 +1396,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1430,12 +1430,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1464,12 +1464,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1498,12 +1498,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1515,12 +1515,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1566,12 +1566,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1583,12 +1583,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1600,12 +1600,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1617,12 +1617,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1651,12 +1651,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1685,12 +1685,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1719,12 +1719,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1770,12 +1770,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1804,12 +1804,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1855,12 +1855,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1889,12 +1889,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1906,12 +1906,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1923,12 +1923,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1940,12 +1940,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -1957,12 +1957,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -1991,12 +1991,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -2008,12 +2008,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -2025,12 +2025,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -2059,12 +2059,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -2076,12 +2076,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -2110,12 +2110,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -2144,12 +2144,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -2161,12 +2161,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2178,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -2195,12 +2195,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -2229,12 +2229,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -2246,12 +2246,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -2263,12 +2263,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -2280,12 +2280,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'value':_'select_all'}</t>
+          <t>select_all</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'value': 'Select All'}</t>
+          <t>Select All</t>
         </is>
       </c>
     </row>
@@ -2297,12 +2297,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'value':_'select_none'}</t>
+          <t>select_none</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'value': 'Select None'}</t>
+          <t>Select None</t>
         </is>
       </c>
     </row>
@@ -2314,12 +2314,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'value':_'select_all_and_sync'}</t>
+          <t>select_all_and_sync</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'value': 'Select All and Sync'}</t>
+          <t>Select All and Sync</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'value':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'value': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'value':_'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'value': 'Audio'}</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
@@ -2365,12 +2365,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{'value':_'image'}</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>{'value': 'Image'}</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
@@ -2382,12 +2382,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{'value':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>{'value': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -2399,12 +2399,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{'value':_'audio'}</t>
+          <t>audio</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>{'value': 'Audio'}</t>
+          <t>Audio</t>
         </is>
       </c>
     </row>
@@ -2416,12 +2416,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{'value':_'image'}</t>
+          <t>image</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>{'value': 'Image'}</t>
+          <t>Image</t>
         </is>
       </c>
     </row>
